--- a/medford_kolposkopy.xlsx
+++ b/medford_kolposkopy.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1188,6 +1188,82 @@
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_06</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Сколько стоит кольпоскоп?</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>kolposkopy</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>FAQ_07</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>170</v>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Сколько дней заживает после кольпоскопии?</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>kolposkopy</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>

--- a/medford_kolposkopy.xlsx
+++ b/medford_kolposkopy.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Кольпоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Sometech, ATMOS, Karl Kaps — всего 20 позиций.</t>
+          <t>Кольпоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Sometech, ATMOS, Karl Kaps.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_kolposkopy.xlsx
+++ b/medford_kolposkopy.xlsx
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать кольпоскопы для клиники?</t>
+          <t>Чем видеокольпоскоп отличается от оптического?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Тип кольпоскопа, Штатив, Страна производства, Производитель). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Оптический кольпоскоп предполагает осмотр напрямую через окуляры. Видеокольпоскоп оснащён камерой и выводит изображение на монитор, что позволяет документировать осмотр, делать снимки, показывать картинку пациенту и транслировать на несколько экранов. Цифровые модели дополнительно сохраняют и обрабатывают изображения.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Какое увеличение нужно для клиники?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Современные модели дают увеличение в широком диапазоне. Для рутинных исследований обычно достаточно 10–15-кратного, а более высокое требуется для детального изучения мелких структур и сосудистого рисунка. Оптимальную кратность под задачи приёма и методику осмотра определяет врач; для приёма важнее стабильная картинка и удобный шаг увеличения.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Что даёт зелёный фильтр в кольпоскопе?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены Sometech, ATMOS, Karl Kaps. Подберём модель под ваши задачи, совместимость и бюджет.</t>
+          <t>Зелёный (бескрасный) светофильтр повышает контраст сосудистого рисунка тканей, поэтому его применяют при расширенной кольпоскопии для оценки сосудов. Наличие фильтра — полезная опция при углублённой диагностике; необходимость его использования в конкретном случае решает врач.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>Какой штатив выбрать?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>В каталоге есть напольные мобильные, консольные и прямые штативы. Напольный удобно перемещать между кабинетами, консольный крепится к стене или основанию и экономит место, прямой компактен. Выбор зависит от планировки кабинета, потока пациентов и того, стационарно или мобильно используется прибор.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Нужно ли регистрационное удостоверение?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Да. Кольпоскоп — медицинское изделие, подлежащее обязательной сертификации и регистрации. Для легального применения в клинике нужно действующее регистрационное удостоверение Росздравнадзора; без него прибор нельзя использовать в лицензируемой медицинской деятельности. Наличие и реквизиты РУ уточняйте до покупки у поставщика.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит кольпоскоп?</t>
+          <t>LED или галоген в качестве источника света?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>LED-подсветка долговечнее, экономичнее и меньше нагревается, а также даёт стабильную цветовую температуру, что важно для корректной оценки цвета тканей при осмотре. Галогеновые лампы дешевле в замене, но нагреваются сильнее и раньше меняют оттенок. Большинство современных моделей каталога используют LED.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Сколько дней заживает после кольпоскопии?</t>
+          <t>Совместим ли видеокольпоскоп с моим монитором и ПК?</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Видеокольпоскопы поставляются с камерой и своим или совместимым выводом на монитор, часть моделей работает с ПК и ПО для архива. Совместимость зависит от интерфейсов конкретной модели — сообщите, какое рабочее место планируете использовать, и мы сверим подключение.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Кольпоскопы для оснащения клиник и медицинских учреждений. В каталоге представлены модели брендов Sometech, ATMOS, Karl Kaps.</t>
+          <t>Кольпоскопы — это оптические приборы для увеличенного осмотра шейки матки, влагалища и вульвы в гинекологии. В каталоге представлены бинокулярные оптические модели (ATMOS I View 21 и 31, Karl Kaps Som 52, ZMir ПРИМА и КС-02), цифровые видеокольпоскопы (Kernel 2200A/2200C Full HD, Sometech DCS-102) и видеокомплексы. Штативы различаются: напольные мобильные, консольные и прямые. Приборы дают многократное увеличение исследуемой области, а видеомодели передают картинку на монитор для документирования осмотра.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Сравнение моделей по характеристикам</t>
+          <t>Виды кольпоскопов по визуализации</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое кольпоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -4454,239 +4454,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>04_COMPARE_ROWS — Сравнение моделей по характеристикам</t>
+          <t>04_COMPARE_ROWS — Виды кольпоскопов по визуализации</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Модель</t>
+          <t>Тип</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>Как смотрит врач</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Тип кольпоскопа</t>
+          <t>Документирование</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Штатив</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Страна производства</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Производитель</t>
+          <t>Пример моделей</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Видеокомплекс для кольпоскопов ZMir Прима К Стандарт</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr"/>
+          <t>Оптический</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Напрямую через окуляры</t>
+        </is>
+      </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Опционально, через насадку</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Россия</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>67379</t>
+          <t>ATMOS I View 21/31, Karl Kaps Som 52, ZMir КС-02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sometech Dr. Camscope DCS-102 видеокольпоскоп</t>
+          <t>Видеокольпоскоп</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Sometech</t>
+          <t>На мониторе с камеры</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Цифровой</t>
+          <t>Штатно: снимки, видео, трансляция</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Kernel 2200A/2200C, Sometech DCS-102</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Смотровой кольпоскоп ATMOS I View 21</t>
+          <t>Цифровой</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>ATMOS</t>
+          <t>На мониторе, с обработкой</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Бинокулярный</t>
+          <t>Сохранение и обработка изображений</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Напольный, мобильный</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Смотровой кольпоскоп ATMOS I View 31</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>ATMOS</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Бинокулярный</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Напольный, мобильный</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Кольпоскоп ZMir ПРИМА К (консольный)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr"/>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Бинокулярный</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Консольный</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Кольпоскоп НИЦ Сканер МК-300</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr"/>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Бинокулярный</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Консольный</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Kernel KN-2200, Kernel 2200A Full HD</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4698,7 +4572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5024,12 +4898,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Выберите способ визуализации</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается кольпоскопы: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Оптические кольпоскопы позволяют смотреть напрямую через окуляры и стоят дешевле. Видеокольпоскопы (Kernel 2200A, Sometech DCS-102) оснащены камерой и выводят картинку на монитор — это документирование, снимки и показ пациенту. Цифровые модели дополнительно сохраняют и обрабатывают изображения.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -5069,12 +4943,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Определите тип оптической системы</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Монокулярные дают плоскую картинку и уступают в качестве. Бинокулярные (ATMOS I View, ZMir КС-02, Karl Kaps Som 52) создают стереоскопический эффект и точнее передают глубину тканей. Тринокулярные имеют третий порт под видеосистему. Для большинства задач берут бинокулярную схему.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -5114,12 +4988,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Подберите тип штатива под кабинет</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Тип кольпоскопа, Штатив, Страна производства, Производитель. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>В каталоге штативы напольные мобильные, консольные и прямые. Напольный на колёсах легко перемещать между кабинетами. Консольный крепят к стене или основанию, он экономит место. Прямой штатив компактен для небольшого кабинета. Выбор зависит от планировки и потока пациентов.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -5159,12 +5033,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените увеличение и источник света</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость. В каталоге: Sometech, ATMOS, Karl Kaps.</t>
+          <t>Для рутинных исследований обычно достаточно 10–15-кратного увеличения, большее нужно для детального изучения структур. Источник света чаще LED: он долговечнее галогена, экономичнее и меньше нагревается, а также даёт стабильную цветовую температуру, важную для оценки тканей.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -5204,12 +5078,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Проверьте наличие фильтров и функций</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Зелёный (бескрасный) фильтр улучшает визуализацию сосудистого рисунка и полезен при расширенной кольпоскопии. Уточните возможность фото- и видеозаписи, вывод на несколько мониторов, регулировку фокусного расстояния и автоклавируемость узлов. Для видеокомплексов проверьте состав: камера, монитор, программное обеспечение для архива и обработки снимков.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -5249,12 +5123,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Уточните регистрацию и комплектность</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Кольпоскоп подлежит обязательной регистрации: запросите действующее регистрационное удостоверение Росздравнадзора. Уточните комплект штатива, оптики, кабелей и ПО для видеомоделей, наличие расходников и запасных ламп. Эти позиции определяют готовность прибора к приёму, корректность обработки и легальность применения в клинике.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -5304,7 +5178,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Кольпоскопы подбирают под задачи отделения и совместимость с имеющимся оборудованием. В нашем каталоге представлены Sometech, ATMOS, Karl Kaps. При выборе обращают внимание на тип кольпоскопа, штатив, страна производства, производитель, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>В кольпоскопе для клиники я советую отталкиваться от формата работы. Если врачу важно документировать осмотр и показывать картинку, берут видеокольпоскоп с выводом на монитор; для классического приёма достаточно бинокулярной оптической модели. LED-подсветку я предпочитаю галогену за стабильную цветовую температуру и меньший нагрев. Тип штатива — напольный, консольный или прямой — подбирают под планировку кабинета и поток пациентов.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -5588,13 +5462,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое кольпоскопы</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Кольпоскопы — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели брендов Sometech, ATMOS, Karl Kaps. Подберём вариант под задачи вашего отделения.</t>
+          <t>Кольпоскоп — прибор для увеличенного осмотра шейки матки, влагалища и вульвы. По визуализации различают оптические модели с осмотром через окуляры, видеокольпоскопы с камерой и выводом на монитор и цифровые системы с сохранением снимков. По оптике бывают монокулярные, бинокулярные и тринокулярные, по установке — напольные, консольные и прямые штативы. При выборе смотрят на увеличение, источник света (чаще LED), фокусное расстояние и наличие зелёного фильтра для оценки сосудистого рисунка. Прибор подлежит обязательной регистрации в Росздравнадзоре как медицинское изделие.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -5631,13 +5505,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое кольпоскоп</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Тип кольпоскопа, Штатив, Страна производства, Производитель), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Кольпоскоп — специализированный прибор, который в гинекологии используют для детального увеличенного осмотра шейки матки, влагалища и вульвы. Многократное увеличение позволяет заметить изменения тканей, невидимые при обычном осмотре, что важно для ранней диагностики патологий, включая предраковые состояния. С кольпоскопом также проводят расширенные тесты и прицельные манипуляции.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -5674,13 +5548,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Виды кольпоскопов</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>По способу визуализации выделяют оптические (осмотр через окуляры), видеокольпоскопы (камера и вывод на монитор) и цифровые модели. По оптической системе — монокулярные, бинокулярные (стереоскопическая картинка) и тринокулярные с портом под видео. По способу установки — напольные, консольные и настенные. Классификация помогает подобрать прибор под формат кабинета.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -5717,13 +5591,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Ключевые характеристики при выборе</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>При подборе смотрят на увеличение (для рутины достаточно 10–15х), источник света (LED предпочтительнее галогена по стабильности и нагреву), фокусное расстояние и эргономику штатива. Важны фильтры — зелёный улучшает визуализацию сосудов — и возможность фото- и видеозаписи. Для видеомоделей значим состав видеокомплекса и вывод на мониторы.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -5740,6 +5614,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Бренды в каталоге</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Каталог включает бинокулярные оптические кольпоскопы ATMOS (I View 21 и 31), Karl Kaps Som 52, отечественные ZMir (ПРИМА, КС-01, КС-02, в том числе ZOOM), НИЦ Сканер МК-300, а также цифровые видеокольпоскопы Kernel (2200A, 2200C, KN-2200) и Sometech Dr. Camscope DCS-102. Есть готовые видеокомплексы на базе кольпоскопов.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>kolposkopy</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
